--- a/data/base/Backlog_46.xlsx
+++ b/data/base/Backlog_46.xlsx
@@ -5,20 +5,20 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\netuno\Departamentos\GTI\Governança de TI\Governança Adriano\Backlog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franciscoj\Python_Initial\Pyhton_Web\data\base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8BA34B27-B6F7-4756-9011-9F0E7290AFA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7EDE464-CE8C-45EF-9B14-4C934C86E6E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-990" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="273" xr2:uid="{89A3EF9E-2AF9-420D-85DF-9BB5B68F651F}"/>
   </bookViews>
   <sheets>
     <sheet name="ITI" sheetId="2" r:id="rId1"/>
     <sheet name="SPN" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$26</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$J$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ITI!$A$1:$K$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">SPN!$A$1:$K$14</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -97,9 +97,6 @@
     <t>Lourival Silva</t>
   </si>
   <si>
-    <t>Erick Silva</t>
-  </si>
-  <si>
     <t>Felipe Nascimento</t>
   </si>
   <si>
@@ -149,6 +146,9 @@
   </si>
   <si>
     <t>Resolvido</t>
+  </si>
+  <si>
+    <t>Erick da Silva</t>
   </si>
 </sst>
 </file>
@@ -661,7 +661,7 @@
         <v>11</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C2" s="9">
         <v>2025</v>
@@ -685,7 +685,7 @@
         <v>45978</v>
       </c>
       <c r="J2" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K2" s="9" t="s">
         <v>13</v>
@@ -696,7 +696,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="C3" s="9">
         <v>2025</v>
@@ -711,7 +711,7 @@
         <v>45982</v>
       </c>
       <c r="G3" s="9">
-        <v>5665</v>
+        <v>5625</v>
       </c>
       <c r="H3" s="3">
         <v>45962</v>
@@ -720,7 +720,7 @@
         <v>45978</v>
       </c>
       <c r="J3" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K3" s="9" t="s">
         <v>13</v>
@@ -731,7 +731,7 @@
         <v>11</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C4" s="9">
         <v>2025</v>
@@ -746,7 +746,7 @@
         <v>45982</v>
       </c>
       <c r="G4" s="9">
-        <v>5650</v>
+        <v>5611</v>
       </c>
       <c r="H4" s="3">
         <v>45962</v>
@@ -755,7 +755,7 @@
         <v>45978</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K4" s="9" t="s">
         <v>13</v>
@@ -766,7 +766,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C5" s="9">
         <v>2025</v>
@@ -781,7 +781,7 @@
         <v>45982</v>
       </c>
       <c r="G5" s="9">
-        <v>5639</v>
+        <v>5587</v>
       </c>
       <c r="H5" s="3">
         <v>45962</v>
@@ -790,7 +790,7 @@
         <v>45978</v>
       </c>
       <c r="J5" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K5" s="9" t="s">
         <v>13</v>
@@ -801,7 +801,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="9">
         <v>2025</v>
@@ -816,7 +816,7 @@
         <v>45982</v>
       </c>
       <c r="G6" s="9">
-        <v>5631</v>
+        <v>5426</v>
       </c>
       <c r="H6" s="3">
         <v>45962</v>
@@ -825,7 +825,7 @@
         <v>45978</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K6" s="9" t="s">
         <v>13</v>
@@ -836,7 +836,7 @@
         <v>11</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="9">
         <v>2025</v>
@@ -851,7 +851,7 @@
         <v>45982</v>
       </c>
       <c r="G7" s="9">
-        <v>5625</v>
+        <v>5361</v>
       </c>
       <c r="H7" s="3">
         <v>45962</v>
@@ -860,7 +860,7 @@
         <v>45978</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K7" s="9" t="s">
         <v>13</v>
@@ -871,7 +871,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C8" s="9">
         <v>2025</v>
@@ -886,7 +886,7 @@
         <v>45982</v>
       </c>
       <c r="G8" s="9">
-        <v>5611</v>
+        <v>5328</v>
       </c>
       <c r="H8" s="3">
         <v>45962</v>
@@ -895,7 +895,7 @@
         <v>45978</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>13</v>
@@ -906,7 +906,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C9" s="9">
         <v>2025</v>
@@ -921,7 +921,7 @@
         <v>45982</v>
       </c>
       <c r="G9" s="9">
-        <v>5591</v>
+        <v>5392</v>
       </c>
       <c r="H9" s="3">
         <v>45962</v>
@@ -930,7 +930,7 @@
         <v>45978</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>13</v>
@@ -941,7 +941,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C10" s="9">
         <v>2025</v>
@@ -956,16 +956,16 @@
         <v>45982</v>
       </c>
       <c r="G10" s="9">
-        <v>5590</v>
+        <v>4677</v>
       </c>
       <c r="H10" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I10" s="2">
         <v>45978</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K10" s="9" t="s">
         <v>13</v>
@@ -976,7 +976,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="C11" s="9">
         <v>2025</v>
@@ -991,16 +991,16 @@
         <v>45982</v>
       </c>
       <c r="G11" s="9">
-        <v>5587</v>
+        <v>4134</v>
       </c>
       <c r="H11" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I11" s="2">
         <v>45978</v>
       </c>
       <c r="J11" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K11" s="9" t="s">
         <v>13</v>
@@ -1011,7 +1011,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C12" s="9">
         <v>2025</v>
@@ -1026,16 +1026,16 @@
         <v>45982</v>
       </c>
       <c r="G12" s="9">
-        <v>5585</v>
+        <v>3264</v>
       </c>
       <c r="H12" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I12" s="2">
         <v>45978</v>
       </c>
       <c r="J12" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K12" s="9" t="s">
         <v>13</v>
@@ -1046,7 +1046,7 @@
         <v>11</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C13" s="9">
         <v>2025</v>
@@ -1061,7 +1061,7 @@
         <v>45982</v>
       </c>
       <c r="G13" s="9">
-        <v>5579</v>
+        <v>5387</v>
       </c>
       <c r="H13" s="3">
         <v>45962</v>
@@ -1070,7 +1070,7 @@
         <v>45978</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K13" s="9" t="s">
         <v>13</v>
@@ -1081,7 +1081,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14" s="9">
         <v>2025</v>
@@ -1096,7 +1096,7 @@
         <v>45982</v>
       </c>
       <c r="G14" s="9">
-        <v>5576</v>
+        <v>5591</v>
       </c>
       <c r="H14" s="3">
         <v>45962</v>
@@ -1105,7 +1105,7 @@
         <v>45978</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>13</v>
@@ -1116,7 +1116,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C15" s="9">
         <v>2025</v>
@@ -1131,7 +1131,7 @@
         <v>45982</v>
       </c>
       <c r="G15" s="9">
-        <v>5564</v>
+        <v>5585</v>
       </c>
       <c r="H15" s="3">
         <v>45962</v>
@@ -1140,7 +1140,7 @@
         <v>45978</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>13</v>
@@ -1151,7 +1151,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" s="9">
         <v>2025</v>
@@ -1166,7 +1166,7 @@
         <v>45982</v>
       </c>
       <c r="G16" s="9">
-        <v>5559</v>
+        <v>5542</v>
       </c>
       <c r="H16" s="3">
         <v>45962</v>
@@ -1175,7 +1175,7 @@
         <v>45978</v>
       </c>
       <c r="J16" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K16" s="9" t="s">
         <v>13</v>
@@ -1186,7 +1186,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C17" s="9">
         <v>2025</v>
@@ -1201,7 +1201,7 @@
         <v>45982</v>
       </c>
       <c r="G17" s="9">
-        <v>5547</v>
+        <v>5540</v>
       </c>
       <c r="H17" s="3">
         <v>45962</v>
@@ -1210,7 +1210,7 @@
         <v>45978</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K17" s="9" t="s">
         <v>13</v>
@@ -1221,7 +1221,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C18" s="9">
         <v>2025</v>
@@ -1236,7 +1236,7 @@
         <v>45982</v>
       </c>
       <c r="G18" s="9">
-        <v>5543</v>
+        <v>5532</v>
       </c>
       <c r="H18" s="3">
         <v>45962</v>
@@ -1245,7 +1245,7 @@
         <v>45978</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K18" s="9" t="s">
         <v>13</v>
@@ -1256,7 +1256,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C19" s="9">
         <v>2025</v>
@@ -1271,7 +1271,7 @@
         <v>45982</v>
       </c>
       <c r="G19" s="9">
-        <v>5542</v>
+        <v>5440</v>
       </c>
       <c r="H19" s="3">
         <v>45962</v>
@@ -1280,7 +1280,7 @@
         <v>45978</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K19" s="9" t="s">
         <v>13</v>
@@ -1291,7 +1291,7 @@
         <v>11</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C20" s="9">
         <v>2025</v>
@@ -1306,7 +1306,7 @@
         <v>45982</v>
       </c>
       <c r="G20" s="9">
-        <v>5540</v>
+        <v>5435</v>
       </c>
       <c r="H20" s="3">
         <v>45962</v>
@@ -1315,7 +1315,7 @@
         <v>45978</v>
       </c>
       <c r="J20" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K20" s="9" t="s">
         <v>13</v>
@@ -1326,7 +1326,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C21" s="9">
         <v>2025</v>
@@ -1341,7 +1341,7 @@
         <v>45982</v>
       </c>
       <c r="G21" s="9">
-        <v>5533</v>
+        <v>5200</v>
       </c>
       <c r="H21" s="3">
         <v>45962</v>
@@ -1350,7 +1350,7 @@
         <v>45978</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K21" s="9" t="s">
         <v>13</v>
@@ -1361,7 +1361,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C22" s="9">
         <v>2025</v>
@@ -1376,7 +1376,7 @@
         <v>45982</v>
       </c>
       <c r="G22" s="9">
-        <v>5532</v>
+        <v>5191</v>
       </c>
       <c r="H22" s="3">
         <v>45962</v>
@@ -1385,7 +1385,7 @@
         <v>45978</v>
       </c>
       <c r="J22" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K22" s="9" t="s">
         <v>13</v>
@@ -1396,7 +1396,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="C23" s="9">
         <v>2025</v>
@@ -1411,7 +1411,7 @@
         <v>45982</v>
       </c>
       <c r="G23" s="9">
-        <v>5515</v>
+        <v>5172</v>
       </c>
       <c r="H23" s="3">
         <v>45962</v>
@@ -1420,7 +1420,7 @@
         <v>45978</v>
       </c>
       <c r="J23" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K23" s="9" t="s">
         <v>13</v>
@@ -1431,7 +1431,7 @@
         <v>11</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C24" s="9">
         <v>2025</v>
@@ -1446,7 +1446,7 @@
         <v>45982</v>
       </c>
       <c r="G24" s="9">
-        <v>5448</v>
+        <v>5157</v>
       </c>
       <c r="H24" s="3">
         <v>45962</v>
@@ -1455,7 +1455,7 @@
         <v>45978</v>
       </c>
       <c r="J24" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K24" s="9" t="s">
         <v>13</v>
@@ -1466,7 +1466,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C25" s="9">
         <v>2025</v>
@@ -1481,7 +1481,7 @@
         <v>45982</v>
       </c>
       <c r="G25" s="9">
-        <v>5440</v>
+        <v>5055</v>
       </c>
       <c r="H25" s="3">
         <v>45962</v>
@@ -1501,7 +1501,7 @@
         <v>11</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="C26" s="9">
         <v>2025</v>
@@ -1516,7 +1516,7 @@
         <v>45982</v>
       </c>
       <c r="G26" s="9">
-        <v>5435</v>
+        <v>5016</v>
       </c>
       <c r="H26" s="3">
         <v>45962</v>
@@ -1525,7 +1525,7 @@
         <v>45978</v>
       </c>
       <c r="J26" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>13</v>
@@ -1536,7 +1536,7 @@
         <v>11</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C27" s="9">
         <v>2025</v>
@@ -1551,7 +1551,7 @@
         <v>45982</v>
       </c>
       <c r="G27" s="9">
-        <v>5426</v>
+        <v>4968</v>
       </c>
       <c r="H27" s="3">
         <v>45962</v>
@@ -1560,7 +1560,7 @@
         <v>45978</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>13</v>
@@ -1571,7 +1571,7 @@
         <v>11</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C28" s="9">
         <v>2025</v>
@@ -1586,7 +1586,7 @@
         <v>45982</v>
       </c>
       <c r="G28" s="9">
-        <v>5392</v>
+        <v>4944</v>
       </c>
       <c r="H28" s="3">
         <v>45962</v>
@@ -1595,7 +1595,7 @@
         <v>45978</v>
       </c>
       <c r="J28" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K28" s="9" t="s">
         <v>13</v>
@@ -1606,7 +1606,7 @@
         <v>11</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C29" s="9">
         <v>2025</v>
@@ -1621,7 +1621,7 @@
         <v>45982</v>
       </c>
       <c r="G29" s="9">
-        <v>5387</v>
+        <v>4814</v>
       </c>
       <c r="H29" s="3">
         <v>45962</v>
@@ -1641,7 +1641,7 @@
         <v>11</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C30" s="9">
         <v>2025</v>
@@ -1656,7 +1656,7 @@
         <v>45982</v>
       </c>
       <c r="G30" s="9">
-        <v>5383</v>
+        <v>5533</v>
       </c>
       <c r="H30" s="3">
         <v>45962</v>
@@ -1665,7 +1665,7 @@
         <v>45978</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K30" s="9" t="s">
         <v>13</v>
@@ -1676,7 +1676,7 @@
         <v>11</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C31" s="9">
         <v>2025</v>
@@ -1691,7 +1691,7 @@
         <v>45982</v>
       </c>
       <c r="G31" s="9">
-        <v>5376</v>
+        <v>5383</v>
       </c>
       <c r="H31" s="3">
         <v>45962</v>
@@ -1700,7 +1700,7 @@
         <v>45978</v>
       </c>
       <c r="J31" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K31" s="9" t="s">
         <v>13</v>
@@ -1711,7 +1711,7 @@
         <v>11</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C32" s="9">
         <v>2025</v>
@@ -1735,7 +1735,7 @@
         <v>45978</v>
       </c>
       <c r="J32" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>13</v>
@@ -1746,7 +1746,7 @@
         <v>11</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C33" s="9">
         <v>2025</v>
@@ -1761,7 +1761,7 @@
         <v>45982</v>
       </c>
       <c r="G33" s="9">
-        <v>5361</v>
+        <v>5287</v>
       </c>
       <c r="H33" s="3">
         <v>45962</v>
@@ -1770,7 +1770,7 @@
         <v>45978</v>
       </c>
       <c r="J33" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>13</v>
@@ -1781,7 +1781,7 @@
         <v>11</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="C34" s="9">
         <v>2025</v>
@@ -1796,7 +1796,7 @@
         <v>45982</v>
       </c>
       <c r="G34" s="9">
-        <v>5328</v>
+        <v>4736</v>
       </c>
       <c r="H34" s="3">
         <v>45962</v>
@@ -1805,7 +1805,7 @@
         <v>45978</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K34" s="9" t="s">
         <v>13</v>
@@ -1816,7 +1816,7 @@
         <v>11</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C35" s="9">
         <v>2025</v>
@@ -1831,16 +1831,16 @@
         <v>45982</v>
       </c>
       <c r="G35" s="9">
-        <v>5304</v>
+        <v>4319</v>
       </c>
       <c r="H35" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I35" s="2">
         <v>45978</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K35" s="9" t="s">
         <v>13</v>
@@ -1851,7 +1851,7 @@
         <v>11</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C36" s="9">
         <v>2025</v>
@@ -1866,7 +1866,7 @@
         <v>45982</v>
       </c>
       <c r="G36" s="9">
-        <v>5287</v>
+        <v>5631</v>
       </c>
       <c r="H36" s="3">
         <v>45962</v>
@@ -1875,7 +1875,7 @@
         <v>45978</v>
       </c>
       <c r="J36" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K36" s="9" t="s">
         <v>13</v>
@@ -1886,7 +1886,7 @@
         <v>11</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C37" s="9">
         <v>2025</v>
@@ -1901,7 +1901,7 @@
         <v>45982</v>
       </c>
       <c r="G37" s="9">
-        <v>5259</v>
+        <v>5376</v>
       </c>
       <c r="H37" s="3">
         <v>45962</v>
@@ -1910,7 +1910,7 @@
         <v>45978</v>
       </c>
       <c r="J37" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K37" s="9" t="s">
         <v>13</v>
@@ -1921,7 +1921,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C38" s="9">
         <v>2025</v>
@@ -1936,7 +1936,7 @@
         <v>45982</v>
       </c>
       <c r="G38" s="9">
-        <v>5205</v>
+        <v>5650</v>
       </c>
       <c r="H38" s="3">
         <v>45962</v>
@@ -1945,7 +1945,7 @@
         <v>45978</v>
       </c>
       <c r="J38" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K38" s="9" t="s">
         <v>13</v>
@@ -1956,7 +1956,7 @@
         <v>11</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C39" s="9">
         <v>2025</v>
@@ -1971,7 +1971,7 @@
         <v>45982</v>
       </c>
       <c r="G39" s="9">
-        <v>5200</v>
+        <v>5515</v>
       </c>
       <c r="H39" s="3">
         <v>45962</v>
@@ -1980,7 +1980,7 @@
         <v>45978</v>
       </c>
       <c r="J39" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K39" s="9" t="s">
         <v>13</v>
@@ -1991,7 +1991,7 @@
         <v>11</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C40" s="9">
         <v>2025</v>
@@ -2006,7 +2006,7 @@
         <v>45982</v>
       </c>
       <c r="G40" s="9">
-        <v>5191</v>
+        <v>5665</v>
       </c>
       <c r="H40" s="3">
         <v>45962</v>
@@ -2015,7 +2015,7 @@
         <v>45978</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K40" s="9" t="s">
         <v>13</v>
@@ -2026,7 +2026,7 @@
         <v>11</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C41" s="9">
         <v>2025</v>
@@ -2041,7 +2041,7 @@
         <v>45982</v>
       </c>
       <c r="G41" s="9">
-        <v>5185</v>
+        <v>5579</v>
       </c>
       <c r="H41" s="3">
         <v>45962</v>
@@ -2050,7 +2050,7 @@
         <v>45978</v>
       </c>
       <c r="J41" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K41" s="9" t="s">
         <v>13</v>
@@ -2061,7 +2061,7 @@
         <v>11</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C42" s="9">
         <v>2025</v>
@@ -2076,7 +2076,7 @@
         <v>45982</v>
       </c>
       <c r="G42" s="9">
-        <v>5172</v>
+        <v>5564</v>
       </c>
       <c r="H42" s="3">
         <v>45962</v>
@@ -2085,7 +2085,7 @@
         <v>45978</v>
       </c>
       <c r="J42" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K42" s="9" t="s">
         <v>13</v>
@@ -2096,7 +2096,7 @@
         <v>11</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C43" s="9">
         <v>2025</v>
@@ -2111,7 +2111,7 @@
         <v>45982</v>
       </c>
       <c r="G43" s="9">
-        <v>5157</v>
+        <v>5547</v>
       </c>
       <c r="H43" s="3">
         <v>45962</v>
@@ -2120,7 +2120,7 @@
         <v>45978</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K43" s="9" t="s">
         <v>13</v>
@@ -2131,7 +2131,7 @@
         <v>11</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C44" s="9">
         <v>2025</v>
@@ -2146,7 +2146,7 @@
         <v>45982</v>
       </c>
       <c r="G44" s="9">
-        <v>5055</v>
+        <v>5543</v>
       </c>
       <c r="H44" s="3">
         <v>45962</v>
@@ -2166,7 +2166,7 @@
         <v>11</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C45" s="9">
         <v>2025</v>
@@ -2181,7 +2181,7 @@
         <v>45982</v>
       </c>
       <c r="G45" s="9">
-        <v>5016</v>
+        <v>5448</v>
       </c>
       <c r="H45" s="3">
         <v>45962</v>
@@ -2190,7 +2190,7 @@
         <v>45978</v>
       </c>
       <c r="J45" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K45" s="9" t="s">
         <v>13</v>
@@ -2201,7 +2201,7 @@
         <v>11</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C46" s="9">
         <v>2025</v>
@@ -2216,7 +2216,7 @@
         <v>45982</v>
       </c>
       <c r="G46" s="9">
-        <v>4968</v>
+        <v>5259</v>
       </c>
       <c r="H46" s="3">
         <v>45962</v>
@@ -2236,7 +2236,7 @@
         <v>11</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C47" s="9">
         <v>2025</v>
@@ -2251,16 +2251,16 @@
         <v>45982</v>
       </c>
       <c r="G47" s="9">
-        <v>4944</v>
+        <v>3974</v>
       </c>
       <c r="H47" s="3">
-        <v>45962</v>
+        <v>45931</v>
       </c>
       <c r="I47" s="2">
         <v>45978</v>
       </c>
       <c r="J47" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K47" s="9" t="s">
         <v>13</v>
@@ -2271,7 +2271,7 @@
         <v>11</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C48" s="9">
         <v>2025</v>
@@ -2286,7 +2286,7 @@
         <v>45982</v>
       </c>
       <c r="G48" s="9">
-        <v>4814</v>
+        <v>5304</v>
       </c>
       <c r="H48" s="3">
         <v>45962</v>
@@ -2306,7 +2306,7 @@
         <v>11</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C49" s="9">
         <v>2025</v>
@@ -2321,7 +2321,7 @@
         <v>45982</v>
       </c>
       <c r="G49" s="9">
-        <v>4736</v>
+        <v>5185</v>
       </c>
       <c r="H49" s="3">
         <v>45962</v>
@@ -2330,7 +2330,7 @@
         <v>45978</v>
       </c>
       <c r="J49" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K49" s="9" t="s">
         <v>13</v>
@@ -2341,7 +2341,7 @@
         <v>11</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C50" s="9">
         <v>2025</v>
@@ -2356,16 +2356,16 @@
         <v>45982</v>
       </c>
       <c r="G50" s="9">
-        <v>4677</v>
+        <v>5639</v>
       </c>
       <c r="H50" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I50" s="2">
         <v>45978</v>
       </c>
       <c r="J50" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K50" s="9" t="s">
         <v>13</v>
@@ -2376,7 +2376,7 @@
         <v>11</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C51" s="9">
         <v>2025</v>
@@ -2391,16 +2391,16 @@
         <v>45982</v>
       </c>
       <c r="G51" s="9">
-        <v>4319</v>
+        <v>5590</v>
       </c>
       <c r="H51" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I51" s="2">
         <v>45978</v>
       </c>
       <c r="J51" s="9" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="K51" s="9" t="s">
         <v>13</v>
@@ -2411,7 +2411,7 @@
         <v>11</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C52" s="9">
         <v>2025</v>
@@ -2426,16 +2426,16 @@
         <v>45982</v>
       </c>
       <c r="G52" s="9">
-        <v>4134</v>
+        <v>5205</v>
       </c>
       <c r="H52" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I52" s="2">
         <v>45978</v>
       </c>
       <c r="J52" s="9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K52" s="9" t="s">
         <v>13</v>
@@ -2446,7 +2446,7 @@
         <v>11</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C53" s="9">
         <v>2025</v>
@@ -2461,16 +2461,16 @@
         <v>45982</v>
       </c>
       <c r="G53" s="9">
-        <v>3974</v>
+        <v>5576</v>
       </c>
       <c r="H53" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I53" s="2">
         <v>45978</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="K53" s="9" t="s">
         <v>13</v>
@@ -2481,7 +2481,7 @@
         <v>11</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="C54" s="9">
         <v>2025</v>
@@ -2496,10 +2496,10 @@
         <v>45982</v>
       </c>
       <c r="G54" s="9">
-        <v>3264</v>
+        <v>5559</v>
       </c>
       <c r="H54" s="3">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="I54" s="2">
         <v>45978</v>
@@ -2512,9 +2512,9 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K26" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K26">
-      <sortCondition ref="B1:B26"/>
+  <autoFilter ref="A1:K54" xr:uid="{69362A46-9E44-40AB-81A2-018EE27C1DC6}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:K54">
+      <sortCondition ref="B1:B54"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2581,7 +2581,7 @@
         <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1">
         <v>2025</v>
@@ -2616,7 +2616,7 @@
         <v>15</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C3" s="1">
         <v>2025</v>
@@ -2640,7 +2640,7 @@
         <v>45978</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>16</v>
@@ -2651,7 +2651,7 @@
         <v>15</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
@@ -2675,7 +2675,7 @@
         <v>45978</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K4" s="1" t="s">
         <v>16</v>
@@ -2686,7 +2686,7 @@
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" s="1">
         <v>2025</v>
@@ -2710,7 +2710,7 @@
         <v>45978</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>16</v>
@@ -2721,7 +2721,7 @@
         <v>15</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1">
         <v>2025</v>
@@ -2745,7 +2745,7 @@
         <v>45978</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K6" s="1" t="s">
         <v>16</v>
@@ -2756,7 +2756,7 @@
         <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" s="1">
         <v>2025</v>
@@ -2780,7 +2780,7 @@
         <v>45978</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K7" s="1" t="s">
         <v>16</v>
@@ -2791,7 +2791,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C8" s="1">
         <v>2025</v>
@@ -2815,7 +2815,7 @@
         <v>45978</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>16</v>
@@ -2826,7 +2826,7 @@
         <v>15</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1">
         <v>2025</v>
@@ -2861,7 +2861,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
@@ -2885,7 +2885,7 @@
         <v>45978</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K10" s="1" t="s">
         <v>16</v>
@@ -2896,7 +2896,7 @@
         <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1">
         <v>2025</v>
@@ -2931,7 +2931,7 @@
         <v>15</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" s="1">
         <v>2025</v>
@@ -2966,7 +2966,7 @@
         <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C13" s="1">
         <v>2025</v>
@@ -2990,7 +2990,7 @@
         <v>45978</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>16</v>
@@ -3001,7 +3001,7 @@
         <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1">
         <v>2025</v>
@@ -3035,6 +3035,7 @@
       <c r="F17" s="13"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K14" xr:uid="{16A6A408-5BF6-4E16-8C71-EC6EB1F5A842}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
